--- a/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260804.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00919/ETF_Investment_Portfolio_20260804.xlsx
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>國產</t>
+          <t>正新</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>117,699,000</t>
+          <t>119,300,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>正新</t>
+          <t>國產</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>119,300,000</t>
+          <t>117,699,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>義隆</t>
+          <t>裕民</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>15,470,000</t>
+          <t>38,623,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>裕民</t>
+          <t>義隆</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>38,623,000</t>
+          <t>15,470,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
